--- a/মাতবাখ-মাদরাসা.xlsx
+++ b/মাতবাখ-মাদরাসা.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programming\11-idarah\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02A31CC4-1BD3-4A9F-B10D-C38B466432BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A4D5666-2F4E-43E5-891E-A9A10138B5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5B9B3438-AC2A-43BD-9F7F-E2DCEDFF52AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B1DFC973-0D30-44C4-B5A2-4AC0C66FCC09}"/>
   </bookViews>
   <sheets>
     <sheet name="অর্থ গ্রহণ" sheetId="1" r:id="rId1"/>
@@ -22,15 +22,14 @@
   <externalReferences>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'অর্থ গ্রহণ'!$B$8:$D$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'বাকির হিসাব'!$A$10:$D$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">মাতবাখ!$A$5:$I$317</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">মাদরাসা!$A$6:$J$319</definedName>
-    <definedName name="খাত">'[1]drop down'!$B$2:$B$5</definedName>
-    <definedName name="সস">'[3]drop down'!$C$2:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'বাকির হিসাব'!$A$9:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">মাতবাখ!$A$5:$I$322</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">মাদরাসা!$A$6:$J$324</definedName>
+    <definedName name="খাত">#REF!</definedName>
+    <definedName name="সস">'[2]drop down'!$C$2:$C$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +60,7 @@
     <author>madrasatul madinah</author>
   </authors>
   <commentList>
-    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{67188E3C-FF35-43E7-92C8-38389EA98CC4}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{032074B1-3CDA-4097-8BDA-E79826CCE04B}">
       <text>
         <r>
           <rPr>
@@ -88,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="386">
   <si>
     <t>অর্থ গ্রহণ ১৪৪৭/৪৮ হিজরী</t>
   </si>
@@ -504,9 +503,24 @@
     <t>মাদরাসা ১৪৪৬/৪৭ হিজরী</t>
   </si>
   <si>
+    <t>খেদমতে খালক</t>
+  </si>
+  <si>
     <t>রবিউস সানিঃ</t>
   </si>
   <si>
+    <t>বাগান-নার্সারী</t>
+  </si>
+  <si>
+    <t>বেলাল</t>
+  </si>
+  <si>
+    <t>হুযূরের ব্যক্তিগত</t>
+  </si>
+  <si>
+    <t>অন্যান্য</t>
+  </si>
+  <si>
     <t>রশীদ</t>
   </si>
   <si>
@@ -567,9 +581,6 @@
     <t>ফ্রিজ মেরামত</t>
   </si>
   <si>
-    <t>হুযূরের ব্যক্তিগত</t>
-  </si>
-  <si>
     <t>মালিবাগ যাতায়াত</t>
   </si>
   <si>
@@ -783,9 +794,6 @@
     <t>ফুল ঝারু</t>
   </si>
   <si>
-    <t>বাগান-নার্সারী</t>
-  </si>
-  <si>
     <t>বাগানের কিটনাশক</t>
   </si>
   <si>
@@ -924,9 +932,6 @@
     <t>চকলেট</t>
   </si>
   <si>
-    <t>খেদমতে খালক</t>
-  </si>
-  <si>
     <t>বিআরবি হাসপাতাল</t>
   </si>
   <si>
@@ -1162,12 +1167,6 @@
   </si>
   <si>
     <t>বকেয়া</t>
-  </si>
-  <si>
-    <t>মামুন</t>
-  </si>
-  <si>
-    <t>বেলাল</t>
   </si>
   <si>
     <t>তারিখ</t>
@@ -2093,9 +2092,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 3" xfId="3" xr:uid="{B7E80BB6-ACEA-4B42-85EA-FE9C68EAAD1A}"/>
+    <cellStyle name="Comma 3" xfId="3" xr:uid="{892221CC-86F9-430B-A5C8-273FE35F1E63}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{52BC3CAB-1BF9-4F35-867D-FE29131B05EA}"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{B5DC3ACF-A4B3-43B1-B091-5C1CE28275AA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2113,64 +2112,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="drop down"/>
-      <sheetName val="অর্থ গ্রহণ"/>
-      <sheetName val="মাতবাখ"/>
-      <sheetName val="মাদরাসা"/>
-      <sheetName val="অন্যান্য খাত"/>
-      <sheetName val="বাকির হিসাব"/>
-      <sheetName val="ড্যাশবোর্ড"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2" t="str">
-            <v>নতুন ভবন</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>দস্তর ভবন</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>মাসজিদ</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>মাকতাব</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="2">
-          <cell r="I2">
-            <v>0</v>
-          </cell>
-          <cell r="J2">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="অর্থ গ্রহন"/>
       <sheetName val="খরচ"/>
@@ -2182,36 +2123,31 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="S2">
-            <v>136375</v>
+            <v>234675</v>
           </cell>
-          <cell r="T2"/>
         </row>
         <row r="4">
           <cell r="F4">
             <v>400000</v>
           </cell>
-          <cell r="G4"/>
           <cell r="S4">
-            <v>100000</v>
+            <v>120000</v>
           </cell>
-          <cell r="T4"/>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>505173</v>
+            <v>760353</v>
           </cell>
-          <cell r="G6"/>
           <cell r="I6">
-            <v>-105173</v>
+            <v>-360353</v>
           </cell>
-          <cell r="J6"/>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="1">
           <cell r="K1">
-            <v>268798</v>
+            <v>405678</v>
           </cell>
         </row>
       </sheetData>
@@ -2222,7 +2158,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2568,7 +2504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA7A17C-3C43-4725-9AE4-027B47CA9927}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA256FA5-A3A7-46F9-90CF-2D8CFCE56B48}">
   <dimension ref="A1:X282"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2650,9 +2586,9 @@
         <f>মাতবাখ!N2+মাদরাসা!N2</f>
         <v>0</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="12" t="e">
         <f>মাতবাখ!O2+মাদরাসা!O2</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="W2" s="9" t="s">
         <v>8</v>
@@ -2680,7 +2616,7 @@
       </c>
       <c r="X3" s="16">
         <f>'বাকির হিসাব'!$C$1</f>
-        <v>233920</v>
+        <v>329160</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="16.149999999999999" customHeight="1">
@@ -2716,7 +2652,7 @@
       </c>
       <c r="X4" s="23">
         <f>X3-X2</f>
-        <v>228276</v>
+        <v>323516</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -2729,9 +2665,9 @@
       </c>
       <c r="K5" s="19"/>
       <c r="L5" s="19"/>
-      <c r="M5" s="12">
+      <c r="M5" s="12" t="e">
         <f>মাতবাখ!J4+মাদরাসা!J4</f>
-        <v>0</v>
+        <v>#REF!</v>
       </c>
       <c r="N5" s="12">
         <f>মাতবাখ!K4+মাদরাসা!K4</f>
@@ -4387,8 +4323,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{541F8139-67D6-4306-9D49-926289C8EEAF}">
-  <dimension ref="A1:Y317"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F35276-0985-4D21-8CE5-8347D50AE8A4}">
+  <dimension ref="A1:Y332"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="9" bestFit="1" customWidth="1"/>
@@ -4413,7 +4349,7 @@
     <col min="21" max="21" width="12.140625" style="9" customWidth="1"/>
     <col min="22" max="22" width="11.5703125" style="9" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="11.7109375" style="9" customWidth="1"/>
-    <col min="24" max="24" width="13.28515625" style="9" customWidth="1"/>
+    <col min="24" max="24" width="9.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12" style="9" bestFit="1" customWidth="1"/>
     <col min="26" max="16384" width="9.140625" style="9"/>
   </cols>
@@ -14548,42 +14484,87 @@
       <c r="J316"/>
       <c r="K316"/>
     </row>
-    <row r="317" spans="1:11" ht="15.6" customHeight="1">
-      <c r="A317" s="9">
-        <v>277</v>
-      </c>
-      <c r="B317" s="7" t="s">
+    <row r="317" spans="1:11">
+      <c r="B317" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C317" s="41">
         <v>2</v>
-      </c>
-      <c r="C317" s="41">
-        <v>13</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E317"/>
-      <c r="F317">
-        <v>1</v>
-      </c>
-      <c r="G317">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H317" s="31"/>
-      <c r="I317" s="57"/>
-      <c r="J317"/>
-      <c r="K317"/>
+    </row>
+    <row r="318" spans="1:11">
+      <c r="B318" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C318" s="41">
+        <v>2</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11">
+      <c r="B319" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C319" s="41">
+        <v>2</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11">
+      <c r="B320" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C320" s="41">
+        <v>2</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="321" spans="2:9">
+      <c r="B321" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C321" s="41">
+        <v>2</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="322" spans="2:9">
+      <c r="B322" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C322" s="41">
+        <v>2</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="332" spans="2:9">
+      <c r="I332" s="35" t="s">
+        <v>124</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I317" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A5:I322" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF117EDA-D77C-488A-A6D9-A6A5FA136E1F}">
-  <dimension ref="A1:X319"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5919D242-265B-4DEA-B2C4-778EBAAD8800}">
+  <dimension ref="A1:X325"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="9"/>
@@ -14595,8 +14576,8 @@
     <col min="7" max="7" width="11" style="3" customWidth="1"/>
     <col min="8" max="8" width="13" style="2" customWidth="1"/>
     <col min="9" max="9" width="14.5703125" style="35" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15" style="9" customWidth="1"/>
     <col min="12" max="12" width="13.28515625" style="9" customWidth="1"/>
     <col min="13" max="13" width="11.140625" style="9" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" style="9" customWidth="1"/>
@@ -14644,8 +14625,13 @@
       <c r="P1" s="38"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="70"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="51"/>
+      <c r="T1" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="51">
+        <f t="shared" ref="U1:U6" si="0">SUMIFS(H:H,I:I,T1)</f>
+        <v>79160</v>
+      </c>
       <c r="X1" s="26"/>
     </row>
     <row r="2" spans="1:24" ht="15.75">
@@ -14670,19 +14656,29 @@
         <f>SUMIFS($H$7:$H$1048576,B$7:B$1048576,N1)</f>
         <v>0</v>
       </c>
-      <c r="O2" s="72">
-        <f>SUMIFS($H$7:$H$1048576,B$7:B$1048576,O1)+'[1]অন্যান্য খাত'!I2</f>
-        <v>0</v>
+      <c r="O2" s="72" t="e">
+        <f>SUMIFS($H$7:$H$1048576,B$7:B$1048576,O1)+#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="P2" s="39"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="73"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="51"/>
+      <c r="Q2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="R2" s="73">
+        <f>SUMIFS(H:H,D:D,Q2)</f>
+        <v>57160</v>
+      </c>
+      <c r="T2" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="51">
+        <f t="shared" si="0"/>
+        <v>16080</v>
+      </c>
     </row>
     <row r="3" spans="1:24" ht="21" customHeight="1">
       <c r="J3" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>13</v>
@@ -14699,17 +14695,27 @@
       <c r="O3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="73"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="51"/>
+      <c r="Q3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="R3" s="73">
+        <f>SUMIFS(H:H,D:D,Q3)</f>
+        <v>2420</v>
+      </c>
+      <c r="T3" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="U3" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:24" ht="16.899999999999999" customHeight="1">
       <c r="H4" s="75"/>
       <c r="I4" s="76"/>
-      <c r="J4" s="74">
-        <f>SUMIFS($H$7:$H$1048576,B$7:B$1048576,J3)+'[1]অন্যান্য খাত'!J2</f>
-        <v>0</v>
+      <c r="J4" s="74" t="e">
+        <f>SUMIFS($H$7:$H$1048576,B$7:B$1048576,J3)+#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="K4" s="72">
         <f>SUMIFS($H$7:$H$1048576,B$7:B$1048576,K3)</f>
@@ -14732,10 +14738,20 @@
         <v>0</v>
       </c>
       <c r="P4" s="77"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="73"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="51"/>
+      <c r="Q4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="73">
+        <f>SUMIFS(H:H,D:D,Q4)+মাতবাখ!S3</f>
+        <v>4000</v>
+      </c>
+      <c r="T4" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="U4" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:24" ht="16.899999999999999" customHeight="1">
       <c r="H5" s="75"/>
@@ -14747,10 +14763,20 @@
       <c r="N5" s="72"/>
       <c r="O5" s="72"/>
       <c r="P5" s="77"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="73"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="51"/>
+      <c r="Q5" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="R5" s="73">
+        <f>SUMIFS(H:H,D:D,Q5)</f>
+        <v>76200</v>
+      </c>
+      <c r="T5" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="U5" s="51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:24" ht="19.899999999999999" customHeight="1">
       <c r="B6" s="27" t="s">
@@ -14776,9 +14802,22 @@
         <v>43</v>
       </c>
       <c r="J6" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="U6" s="16"/>
+        <v>144</v>
+      </c>
+      <c r="Q6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6" s="9">
+        <f>SUMIFS(H:H,I:I,Q6)</f>
+        <v>0</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="U6" s="16">
+        <f t="shared" si="0"/>
+        <v>11755</v>
+      </c>
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1">
       <c r="A7" s="9">
@@ -14791,7 +14830,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -14800,7 +14839,7 @@
         <v>1000</v>
       </c>
       <c r="H7" s="31">
-        <f t="shared" ref="H7:H16" si="0">F7*G7</f>
+        <f t="shared" ref="H7:H16" si="1">F7*G7</f>
         <v>1000</v>
       </c>
       <c r="I7" s="1"/>
@@ -14820,10 +14859,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -14832,7 +14871,7 @@
         <v>8552</v>
       </c>
       <c r="H8" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8552</v>
       </c>
       <c r="I8"/>
@@ -14851,7 +14890,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -14860,7 +14899,7 @@
         <v>200</v>
       </c>
       <c r="H9" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="I9"/>
@@ -14876,7 +14915,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -14885,7 +14924,7 @@
         <v>1000</v>
       </c>
       <c r="H10" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
       <c r="I10"/>
@@ -14904,7 +14943,7 @@
         <v>4</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -14913,7 +14952,7 @@
         <v>340</v>
       </c>
       <c r="H11" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>680</v>
       </c>
       <c r="I11"/>
@@ -14932,7 +14971,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="42" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F12">
         <v>2</v>
@@ -14941,7 +14980,7 @@
         <v>450</v>
       </c>
       <c r="H12" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>900</v>
       </c>
       <c r="I12"/>
@@ -14960,7 +14999,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -14969,7 +15008,7 @@
         <v>140</v>
       </c>
       <c r="H13" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>140</v>
       </c>
       <c r="I13"/>
@@ -14997,7 +15036,7 @@
         <v>680</v>
       </c>
       <c r="H14" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>680</v>
       </c>
       <c r="I14"/>
@@ -15027,7 +15066,7 @@
         <v>560</v>
       </c>
       <c r="H15" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16800</v>
       </c>
       <c r="I15"/>
@@ -15046,7 +15085,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F16">
         <v>2.5</v>
@@ -15055,7 +15094,7 @@
         <v>5760</v>
       </c>
       <c r="H16" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14400</v>
       </c>
       <c r="I16" t="s">
@@ -15076,7 +15115,7 @@
         <v>6</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -15106,7 +15145,7 @@
       </c>
       <c r="D18" s="78"/>
       <c r="E18" s="80" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F18" s="81">
         <v>1</v>
@@ -15133,7 +15172,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F19">
         <v>1.5</v>
@@ -15183,7 +15222,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -15283,10 +15322,10 @@
         <v>9</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E25" s="42" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -15311,7 +15350,7 @@
         <v>9</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -15339,7 +15378,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F27">
         <v>20</v>
@@ -15364,7 +15403,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -15386,10 +15425,10 @@
         <v>9</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F29">
         <v>1.5</v>
@@ -15417,7 +15456,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -15445,10 +15484,10 @@
         <v>9</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F31">
         <v>25</v>
@@ -15475,10 +15514,10 @@
         <v>10</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -15503,7 +15542,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F33"/>
       <c r="G33"/>
@@ -15526,10 +15565,10 @@
         <v>10</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -15556,10 +15595,10 @@
         <v>10</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -15584,7 +15623,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -15611,7 +15650,7 @@
         <v>10</v>
       </c>
       <c r="E37" s="42" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -15638,10 +15677,10 @@
         <v>10</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F38">
         <v>25</v>
@@ -15668,7 +15707,7 @@
         <v>11</v>
       </c>
       <c r="E39" s="42" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F39">
         <v>2</v>
@@ -15693,10 +15732,10 @@
         <v>11</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E40" s="42" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F40"/>
       <c r="G40"/>
@@ -15719,7 +15758,7 @@
         <v>11</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -15744,10 +15783,10 @@
         <v>11</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E42" s="42" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -15772,10 +15811,10 @@
         <v>11</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F43">
         <v>2</v>
@@ -15803,10 +15842,10 @@
         <v>11</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E44" s="42" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -15831,7 +15870,7 @@
         <v>11</v>
       </c>
       <c r="E45" s="42" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F45"/>
       <c r="G45"/>
@@ -15854,10 +15893,10 @@
         <v>11</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E46" s="42" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F46"/>
       <c r="G46"/>
@@ -15880,7 +15919,7 @@
         <v>12</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F47"/>
       <c r="G47"/>
@@ -15903,7 +15942,7 @@
         <v>12</v>
       </c>
       <c r="E48" s="42" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F48"/>
       <c r="G48"/>
@@ -15926,7 +15965,7 @@
         <v>12</v>
       </c>
       <c r="E49" s="42" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F49"/>
       <c r="G49"/>
@@ -15949,7 +15988,7 @@
         <v>12</v>
       </c>
       <c r="E50" s="42" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F50"/>
       <c r="G50"/>
@@ -16018,7 +16057,7 @@
         <v>12</v>
       </c>
       <c r="E53" s="42" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F53"/>
       <c r="G53"/>
@@ -16041,7 +16080,7 @@
         <v>12</v>
       </c>
       <c r="E54" s="42" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F54"/>
       <c r="G54"/>
@@ -16064,10 +16103,10 @@
         <v>12</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E55" s="42" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F55"/>
       <c r="G55"/>
@@ -16090,7 +16129,7 @@
         <v>12</v>
       </c>
       <c r="E56" s="42" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F56">
         <v>4</v>
@@ -16117,7 +16156,7 @@
         <v>12</v>
       </c>
       <c r="E57" s="42" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F57">
         <v>5</v>
@@ -16145,7 +16184,7 @@
         <v>12</v>
       </c>
       <c r="E58" s="42" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="F58"/>
       <c r="G58"/>
@@ -16168,7 +16207,7 @@
         <v>12</v>
       </c>
       <c r="E59" s="42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -16193,10 +16232,10 @@
         <v>12</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E60" s="42" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F60">
         <v>25</v>
@@ -16223,7 +16262,7 @@
         <v>13</v>
       </c>
       <c r="E61" s="42" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F61"/>
       <c r="G61"/>
@@ -16246,7 +16285,7 @@
         <v>13</v>
       </c>
       <c r="E62" s="42" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F62"/>
       <c r="G62"/>
@@ -16269,10 +16308,10 @@
         <v>13</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E63" s="42" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F63"/>
       <c r="G63"/>
@@ -16295,10 +16334,10 @@
         <v>13</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E64" s="42" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F64"/>
       <c r="G64"/>
@@ -16321,7 +16360,7 @@
         <v>15</v>
       </c>
       <c r="E65" s="42" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -16346,7 +16385,7 @@
         <v>15</v>
       </c>
       <c r="E66" s="42" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F66">
         <v>3</v>
@@ -16371,7 +16410,7 @@
         <v>15</v>
       </c>
       <c r="E67" s="42" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -16396,7 +16435,7 @@
         <v>15</v>
       </c>
       <c r="E68" s="42" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -16421,10 +16460,10 @@
         <v>15</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E69" s="42" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F69"/>
       <c r="G69"/>
@@ -16447,10 +16486,10 @@
         <v>15</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E70" s="42" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F70"/>
       <c r="G70"/>
@@ -16473,10 +16512,10 @@
         <v>15</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E71" s="42" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F71"/>
       <c r="G71"/>
@@ -16499,7 +16538,7 @@
         <v>15</v>
       </c>
       <c r="E72" s="42" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F72"/>
       <c r="G72"/>
@@ -16522,10 +16561,10 @@
         <v>15</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E73" s="42" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F73"/>
       <c r="G73"/>
@@ -16548,7 +16587,7 @@
         <v>15</v>
       </c>
       <c r="E74" s="42" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F74">
         <v>20</v>
@@ -16578,7 +16617,7 @@
         <v>15</v>
       </c>
       <c r="E75" s="42" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -16605,7 +16644,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="42" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -16632,7 +16671,7 @@
         <v>15</v>
       </c>
       <c r="E77" s="42" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F77">
         <v>200</v>
@@ -16659,7 +16698,7 @@
         <v>15</v>
       </c>
       <c r="E78" s="42" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F78">
         <v>73</v>
@@ -16668,7 +16707,7 @@
         <v>26</v>
       </c>
       <c r="H78" s="31">
-        <f t="shared" ref="H78:H83" si="1">F78*G78</f>
+        <f t="shared" ref="H78:H83" si="2">F78*G78</f>
         <v>1898</v>
       </c>
       <c r="I78" t="s">
@@ -16689,10 +16728,10 @@
         <v>15</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E79" s="42" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F79">
         <v>8</v>
@@ -16701,7 +16740,7 @@
         <v>650</v>
       </c>
       <c r="H79" s="31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5200</v>
       </c>
       <c r="I79" t="s">
@@ -16722,10 +16761,10 @@
         <v>15</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E80" s="42" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F80">
         <v>4</v>
@@ -16734,7 +16773,7 @@
         <v>520</v>
       </c>
       <c r="H80" s="31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2080</v>
       </c>
       <c r="I80" t="s">
@@ -16755,10 +16794,10 @@
         <v>15</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E81" s="42" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F81">
         <v>25</v>
@@ -16767,7 +16806,7 @@
         <v>37</v>
       </c>
       <c r="H81" s="31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>925</v>
       </c>
       <c r="I81" t="s">
@@ -16788,7 +16827,7 @@
         <v>15</v>
       </c>
       <c r="E82" s="42" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F82">
         <v>7</v>
@@ -16797,7 +16836,7 @@
         <v>90</v>
       </c>
       <c r="H82" s="31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>630</v>
       </c>
       <c r="I82" t="s">
@@ -16818,7 +16857,7 @@
         <v>15</v>
       </c>
       <c r="E83" s="42" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -16827,7 +16866,7 @@
         <v>30</v>
       </c>
       <c r="H83" s="31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="I83" t="s">
@@ -16846,10 +16885,10 @@
         <v>15</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E84" s="42" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F84"/>
       <c r="G84"/>
@@ -16872,7 +16911,7 @@
         <v>15</v>
       </c>
       <c r="E85" s="42" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F85">
         <v>7</v>
@@ -16881,7 +16920,7 @@
         <v>550</v>
       </c>
       <c r="H85" s="31">
-        <f t="shared" ref="H85:H92" si="2">F85*G85</f>
+        <f t="shared" ref="H85:H92" si="3">F85*G85</f>
         <v>3850</v>
       </c>
       <c r="I85" t="s">
@@ -16900,7 +16939,7 @@
         <v>15</v>
       </c>
       <c r="E86" s="42" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F86">
         <v>7</v>
@@ -16909,7 +16948,7 @@
         <v>300</v>
       </c>
       <c r="H86" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2100</v>
       </c>
       <c r="I86" t="s">
@@ -16928,10 +16967,10 @@
         <v>15</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E87" s="42" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F87">
         <v>15</v>
@@ -16940,7 +16979,7 @@
         <v>130</v>
       </c>
       <c r="H87" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1950</v>
       </c>
       <c r="I87" t="s">
@@ -16959,10 +16998,10 @@
         <v>15</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E88" s="42" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -16971,7 +17010,7 @@
         <v>280</v>
       </c>
       <c r="H88" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
       <c r="I88" t="s">
@@ -16991,10 +17030,10 @@
         <v>15</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E89" s="42" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F89">
         <v>14</v>
@@ -17003,7 +17042,7 @@
         <v>3700</v>
       </c>
       <c r="H89" s="83">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>51800</v>
       </c>
       <c r="I89" t="s">
@@ -17023,10 +17062,10 @@
         <v>15</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E90" s="42" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F90">
         <v>6</v>
@@ -17035,7 +17074,7 @@
         <v>400</v>
       </c>
       <c r="H90" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2400</v>
       </c>
       <c r="I90" t="s">
@@ -17054,7 +17093,7 @@
         <v>15</v>
       </c>
       <c r="E91" s="42" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F91">
         <v>24</v>
@@ -17063,7 +17102,7 @@
         <v>50</v>
       </c>
       <c r="H91" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1200</v>
       </c>
       <c r="I91" t="s">
@@ -17082,7 +17121,7 @@
         <v>15</v>
       </c>
       <c r="E92" s="42" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F92">
         <v>24</v>
@@ -17091,7 +17130,7 @@
         <v>50</v>
       </c>
       <c r="H92" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1200</v>
       </c>
       <c r="I92" t="s">
@@ -17110,7 +17149,7 @@
         <v>15</v>
       </c>
       <c r="E93" s="42" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F93"/>
       <c r="G93"/>
@@ -17133,7 +17172,7 @@
         <v>15</v>
       </c>
       <c r="E94" s="42" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F94"/>
       <c r="G94"/>
@@ -17156,7 +17195,7 @@
         <v>15</v>
       </c>
       <c r="E95" s="42" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G95"/>
       <c r="H95">
@@ -17178,7 +17217,7 @@
         <v>15</v>
       </c>
       <c r="E96" s="42" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F96"/>
       <c r="G96"/>
@@ -17201,7 +17240,7 @@
         <v>15</v>
       </c>
       <c r="E97" s="42" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F97"/>
       <c r="G97"/>
@@ -17224,7 +17263,7 @@
         <v>15</v>
       </c>
       <c r="E98" s="42" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F98"/>
       <c r="G98"/>
@@ -17247,7 +17286,7 @@
         <v>15</v>
       </c>
       <c r="E99" s="42" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F99"/>
       <c r="G99"/>
@@ -17272,7 +17311,7 @@
         <v>15</v>
       </c>
       <c r="E100" s="42" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F100"/>
       <c r="G100"/>
@@ -17297,7 +17336,7 @@
         <v>15</v>
       </c>
       <c r="E101" s="42" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F101">
         <v>12</v>
@@ -17327,7 +17366,7 @@
         <v>15</v>
       </c>
       <c r="E102" s="42" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F102">
         <v>12</v>
@@ -17357,7 +17396,7 @@
         <v>15</v>
       </c>
       <c r="E103" s="42" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F103">
         <v>24</v>
@@ -17384,7 +17423,7 @@
         <v>15</v>
       </c>
       <c r="E104" s="42" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F104">
         <v>12</v>
@@ -17411,7 +17450,7 @@
         <v>15</v>
       </c>
       <c r="E105" s="42" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F105">
         <v>12</v>
@@ -17437,7 +17476,7 @@
         <v>15</v>
       </c>
       <c r="E106" s="42" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F106">
         <v>5</v>
@@ -17467,7 +17506,7 @@
         <v>15</v>
       </c>
       <c r="E107" s="42" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F107">
         <v>4</v>
@@ -17494,7 +17533,7 @@
         <v>15</v>
       </c>
       <c r="E108" s="42" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F108">
         <v>2</v>
@@ -17521,7 +17560,7 @@
         <v>15</v>
       </c>
       <c r="E109" s="42" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F109">
         <v>56</v>
@@ -17548,7 +17587,7 @@
         <v>15</v>
       </c>
       <c r="E110" s="42" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F110">
         <v>4</v>
@@ -17575,7 +17614,7 @@
         <v>15</v>
       </c>
       <c r="E111" s="42" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F111"/>
       <c r="G111"/>
@@ -17600,7 +17639,7 @@
         <v>15</v>
       </c>
       <c r="E112" s="42" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F112"/>
       <c r="G112"/>
@@ -17625,7 +17664,7 @@
         <v>15</v>
       </c>
       <c r="E113" s="42" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F113">
         <v>3</v>
@@ -17652,7 +17691,7 @@
         <v>15</v>
       </c>
       <c r="E114" s="42" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -17679,7 +17718,7 @@
         <v>15</v>
       </c>
       <c r="E115" s="42" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F115"/>
       <c r="G115"/>
@@ -17704,7 +17743,7 @@
         <v>15</v>
       </c>
       <c r="E116" s="42" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F116">
         <v>3</v>
@@ -17734,7 +17773,7 @@
         <v>15</v>
       </c>
       <c r="E117" s="42" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="F117"/>
       <c r="G117"/>
@@ -17759,7 +17798,7 @@
         <v>15</v>
       </c>
       <c r="E118" s="42" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F118">
         <v>82</v>
@@ -17786,7 +17825,7 @@
         <v>15</v>
       </c>
       <c r="E119" s="42" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F119"/>
       <c r="G119"/>
@@ -17811,7 +17850,7 @@
         <v>15</v>
       </c>
       <c r="E120" s="42" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F120">
         <v>5</v>
@@ -17838,10 +17877,10 @@
         <v>15</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E121" s="42" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F121"/>
       <c r="G121"/>
@@ -17866,7 +17905,7 @@
         <v>15</v>
       </c>
       <c r="E122" s="42" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F122"/>
       <c r="G122"/>
@@ -17891,10 +17930,10 @@
         <v>15</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>231</v>
+        <v>140</v>
       </c>
       <c r="E123" s="42" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F123"/>
       <c r="G123"/>
@@ -17944,7 +17983,7 @@
         <v>15</v>
       </c>
       <c r="E125" s="42" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F125">
         <v>7</v>
@@ -17953,11 +17992,11 @@
         <v>572</v>
       </c>
       <c r="H125" s="31">
-        <f t="shared" ref="H125:H130" si="3">F125*G125</f>
+        <f t="shared" ref="H125:H130" si="4">F125*G125</f>
         <v>4004</v>
       </c>
       <c r="I125" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J125"/>
       <c r="K125"/>
@@ -17974,7 +18013,7 @@
         <v>15</v>
       </c>
       <c r="E126" s="42" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F126">
         <v>10</v>
@@ -17986,7 +18025,7 @@
         <v>2800</v>
       </c>
       <c r="I126" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J126"/>
       <c r="K126"/>
@@ -18003,7 +18042,7 @@
         <v>15</v>
       </c>
       <c r="E127" s="42" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F127">
         <v>5</v>
@@ -18012,11 +18051,11 @@
         <v>164</v>
       </c>
       <c r="H127" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>820</v>
       </c>
       <c r="I127" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J127"/>
       <c r="K127"/>
@@ -18033,7 +18072,7 @@
         <v>15</v>
       </c>
       <c r="E128" s="42" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -18042,11 +18081,11 @@
         <v>500</v>
       </c>
       <c r="H128" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>500</v>
       </c>
       <c r="I128" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J128"/>
       <c r="K128"/>
@@ -18063,7 +18102,7 @@
         <v>15</v>
       </c>
       <c r="E129" s="42" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F129">
         <v>9</v>
@@ -18072,11 +18111,11 @@
         <v>100</v>
       </c>
       <c r="H129" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>900</v>
       </c>
       <c r="I129" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J129"/>
       <c r="L129"/>
@@ -18092,7 +18131,7 @@
         <v>15</v>
       </c>
       <c r="E130" s="42" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F130">
         <v>5</v>
@@ -18101,11 +18140,11 @@
         <v>96</v>
       </c>
       <c r="H130" s="31">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>480</v>
       </c>
       <c r="I130" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J130"/>
       <c r="K130"/>
@@ -18122,7 +18161,7 @@
         <v>15</v>
       </c>
       <c r="E131" s="42" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F131"/>
       <c r="G131">
@@ -18132,7 +18171,7 @@
         <v>200</v>
       </c>
       <c r="I131" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J131"/>
       <c r="K131"/>
@@ -18149,7 +18188,7 @@
         <v>15</v>
       </c>
       <c r="E132" s="42" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F132"/>
       <c r="G132"/>
@@ -18157,7 +18196,7 @@
         <v>300</v>
       </c>
       <c r="I132" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J132"/>
       <c r="K132"/>
@@ -18174,7 +18213,7 @@
         <v>15</v>
       </c>
       <c r="E133" s="42" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F133">
         <v>5</v>
@@ -18183,11 +18222,11 @@
         <v>2350</v>
       </c>
       <c r="H133" s="31">
-        <f t="shared" ref="H133:H161" si="4">F133*G133</f>
+        <f t="shared" ref="H133:H161" si="5">F133*G133</f>
         <v>11750</v>
       </c>
       <c r="I133" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J133"/>
       <c r="K133"/>
@@ -18213,11 +18252,11 @@
         <v>240</v>
       </c>
       <c r="H134" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>240</v>
       </c>
       <c r="I134" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J134"/>
       <c r="K134"/>
@@ -18234,7 +18273,7 @@
         <v>15</v>
       </c>
       <c r="E135" s="42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -18243,11 +18282,11 @@
         <v>200</v>
       </c>
       <c r="H135" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>200</v>
       </c>
       <c r="I135" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J135"/>
       <c r="K135"/>
@@ -18264,7 +18303,7 @@
         <v>15</v>
       </c>
       <c r="E136" s="42" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -18273,11 +18312,11 @@
         <v>500</v>
       </c>
       <c r="H136" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="I136" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J136"/>
       <c r="K136"/>
@@ -18294,7 +18333,7 @@
         <v>16</v>
       </c>
       <c r="E137" s="42" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -18303,11 +18342,11 @@
         <v>510</v>
       </c>
       <c r="H137" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>510</v>
       </c>
       <c r="I137" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J137"/>
       <c r="K137"/>
@@ -18324,10 +18363,10 @@
         <v>16</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E138" s="42" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -18336,11 +18375,11 @@
         <v>1225</v>
       </c>
       <c r="H138" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1225</v>
       </c>
       <c r="I138" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J138"/>
       <c r="K138"/>
@@ -18357,7 +18396,7 @@
         <v>16</v>
       </c>
       <c r="E139" s="42" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F139">
         <v>5</v>
@@ -18366,11 +18405,11 @@
         <v>120</v>
       </c>
       <c r="H139" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>600</v>
       </c>
       <c r="I139" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J139"/>
       <c r="K139"/>
@@ -18387,7 +18426,7 @@
         <v>16</v>
       </c>
       <c r="E140" s="42" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F140">
         <v>12</v>
@@ -18399,7 +18438,7 @@
         <v>200</v>
       </c>
       <c r="I140" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J140"/>
       <c r="K140"/>
@@ -18416,7 +18455,7 @@
         <v>16</v>
       </c>
       <c r="E141" s="42" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -18425,11 +18464,11 @@
         <v>1500</v>
       </c>
       <c r="H141" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1500</v>
       </c>
       <c r="I141" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J141"/>
       <c r="K141"/>
@@ -18446,7 +18485,7 @@
         <v>16</v>
       </c>
       <c r="E142" s="42" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F142">
         <v>50</v>
@@ -18455,11 +18494,11 @@
         <v>80</v>
       </c>
       <c r="H142" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>4000</v>
       </c>
       <c r="I142" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J142"/>
       <c r="K142"/>
@@ -18485,11 +18524,11 @@
         <v>270</v>
       </c>
       <c r="H143" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="I143" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J143"/>
       <c r="K143"/>
@@ -18506,7 +18545,7 @@
         <v>16</v>
       </c>
       <c r="E144" s="42" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -18515,7 +18554,7 @@
         <v>400</v>
       </c>
       <c r="H144" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>400</v>
       </c>
       <c r="I144"/>
@@ -18534,10 +18573,10 @@
         <v>16</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E145" s="42" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -18546,7 +18585,7 @@
         <v>800</v>
       </c>
       <c r="H145" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>800</v>
       </c>
       <c r="I145"/>
@@ -18565,7 +18604,7 @@
         <v>16</v>
       </c>
       <c r="E146" s="42" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -18574,7 +18613,7 @@
         <v>12000</v>
       </c>
       <c r="H146" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12000</v>
       </c>
       <c r="I146"/>
@@ -18593,7 +18632,7 @@
         <v>16</v>
       </c>
       <c r="E147" s="42" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -18602,7 +18641,7 @@
         <v>12000</v>
       </c>
       <c r="H147" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12000</v>
       </c>
       <c r="I147"/>
@@ -18621,7 +18660,7 @@
         <v>16</v>
       </c>
       <c r="E148" s="42" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -18630,7 +18669,7 @@
         <v>240</v>
       </c>
       <c r="H148" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>240</v>
       </c>
       <c r="I148"/>
@@ -18649,10 +18688,10 @@
         <v>16</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E149" s="42" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F149">
         <v>100</v>
@@ -18661,7 +18700,7 @@
         <v>127</v>
       </c>
       <c r="H149" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12700</v>
       </c>
       <c r="I149"/>
@@ -18680,7 +18719,7 @@
         <v>17</v>
       </c>
       <c r="E150" s="42" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F150">
         <v>2</v>
@@ -18689,7 +18728,7 @@
         <v>1492.5</v>
       </c>
       <c r="H150" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2985</v>
       </c>
       <c r="I150" t="s">
@@ -18710,7 +18749,7 @@
         <v>17</v>
       </c>
       <c r="E151" s="42" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F151">
         <v>2</v>
@@ -18719,7 +18758,7 @@
         <v>257.5</v>
       </c>
       <c r="H151" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>515</v>
       </c>
       <c r="I151"/>
@@ -18738,10 +18777,10 @@
         <v>17</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E152" s="42" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -18750,7 +18789,7 @@
         <v>1500</v>
       </c>
       <c r="H152" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1500</v>
       </c>
       <c r="I152"/>
@@ -18769,10 +18808,10 @@
         <v>17</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>231</v>
+        <v>140</v>
       </c>
       <c r="E153" s="42" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -18781,7 +18820,7 @@
         <v>1500</v>
       </c>
       <c r="H153" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1500</v>
       </c>
       <c r="I153"/>
@@ -18800,7 +18839,7 @@
         <v>17</v>
       </c>
       <c r="E154" s="42" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F154">
         <v>50</v>
@@ -18809,11 +18848,11 @@
         <v>25</v>
       </c>
       <c r="H154" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1250</v>
       </c>
       <c r="I154" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J154"/>
       <c r="K154" t="s">
@@ -18832,7 +18871,7 @@
         <v>17</v>
       </c>
       <c r="E155" s="42" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F155">
         <v>2</v>
@@ -18841,7 +18880,7 @@
         <v>780</v>
       </c>
       <c r="H155" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1560</v>
       </c>
       <c r="I155"/>
@@ -18860,7 +18899,7 @@
         <v>17</v>
       </c>
       <c r="E156" s="80" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F156" s="81">
         <v>1</v>
@@ -18869,7 +18908,7 @@
         <v>500</v>
       </c>
       <c r="H156" s="82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="I156"/>
@@ -18888,7 +18927,7 @@
         <v>18</v>
       </c>
       <c r="E157" s="42" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -18897,7 +18936,7 @@
         <v>1200</v>
       </c>
       <c r="H157" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1200</v>
       </c>
       <c r="I157" t="s">
@@ -18920,7 +18959,7 @@
         <v>18</v>
       </c>
       <c r="E158" s="42" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F158">
         <v>4</v>
@@ -18929,7 +18968,7 @@
         <v>310</v>
       </c>
       <c r="H158" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1240</v>
       </c>
       <c r="I158" t="s">
@@ -18952,7 +18991,7 @@
         <v>18</v>
       </c>
       <c r="E159" s="42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -18961,7 +19000,7 @@
         <v>350</v>
       </c>
       <c r="H159" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>350</v>
       </c>
       <c r="I159" t="s">
@@ -18982,7 +19021,7 @@
         <v>18</v>
       </c>
       <c r="E160" s="42" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -18991,7 +19030,7 @@
         <v>3415</v>
       </c>
       <c r="H160" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3415</v>
       </c>
       <c r="I160" t="s">
@@ -19012,10 +19051,10 @@
         <v>18</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E161" s="42" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -19024,7 +19063,7 @@
         <v>1000</v>
       </c>
       <c r="H161" s="31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1000</v>
       </c>
       <c r="I161" t="s">
@@ -19045,10 +19084,10 @@
         <v>18</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E162" s="42" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F162">
         <v>220</v>
@@ -19073,7 +19112,7 @@
         <v>18</v>
       </c>
       <c r="E163" s="42" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F163">
         <v>4</v>
@@ -19101,10 +19140,10 @@
         <v>19</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E164" s="42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F164"/>
       <c r="G164"/>
@@ -19129,7 +19168,7 @@
         <v>19</v>
       </c>
       <c r="E165" s="42" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F165"/>
       <c r="G165"/>
@@ -19154,10 +19193,10 @@
         <v>19</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E166" s="42" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F166"/>
       <c r="G166"/>
@@ -19182,7 +19221,7 @@
         <v>20</v>
       </c>
       <c r="E167" s="42" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F167"/>
       <c r="G167"/>
@@ -19205,7 +19244,7 @@
         <v>20</v>
       </c>
       <c r="E168" s="42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F168"/>
       <c r="G168"/>
@@ -19228,10 +19267,10 @@
         <v>20</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E169" s="42" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -19256,7 +19295,7 @@
         <v>20</v>
       </c>
       <c r="E170" s="42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F170">
         <v>20</v>
@@ -19281,7 +19320,7 @@
         <v>20</v>
       </c>
       <c r="E171" s="42" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F171">
         <v>20</v>
@@ -19306,7 +19345,7 @@
         <v>20</v>
       </c>
       <c r="E172" s="42" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F172"/>
       <c r="G172"/>
@@ -19329,10 +19368,10 @@
         <v>20</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E173" s="42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -19357,7 +19396,7 @@
         <v>20</v>
       </c>
       <c r="E174" s="42" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -19382,7 +19421,7 @@
         <v>20</v>
       </c>
       <c r="E175" s="42" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F175"/>
       <c r="G175"/>
@@ -19405,7 +19444,7 @@
         <v>20</v>
       </c>
       <c r="E176" s="42" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F176"/>
       <c r="G176"/>
@@ -19428,7 +19467,7 @@
         <v>20</v>
       </c>
       <c r="E177" s="42" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F177">
         <v>130</v>
@@ -19453,7 +19492,7 @@
         <v>20</v>
       </c>
       <c r="E178" s="42" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F178">
         <v>2</v>
@@ -19481,7 +19520,7 @@
         <v>20</v>
       </c>
       <c r="E179" s="42" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -19506,7 +19545,7 @@
         <v>20</v>
       </c>
       <c r="E180" s="42" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F180">
         <v>12</v>
@@ -19534,7 +19573,7 @@
         <v>20</v>
       </c>
       <c r="E181" s="42" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F181"/>
       <c r="G181"/>
@@ -19557,7 +19596,7 @@
         <v>20</v>
       </c>
       <c r="E182" s="42" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F182">
         <v>60</v>
@@ -19585,7 +19624,7 @@
         <v>20</v>
       </c>
       <c r="E183" s="42" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F183"/>
       <c r="G183"/>
@@ -19611,7 +19650,7 @@
         <v>20</v>
       </c>
       <c r="E184" s="42" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F184"/>
       <c r="G184"/>
@@ -19634,7 +19673,7 @@
         <v>20</v>
       </c>
       <c r="E185" s="42" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -19662,7 +19701,7 @@
         <v>20</v>
       </c>
       <c r="E186" s="42" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -19690,10 +19729,10 @@
         <v>20</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="E187" s="42" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F187">
         <v>2</v>
@@ -19718,10 +19757,10 @@
         <v>20</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E188" s="42" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -19745,7 +19784,7 @@
         <v>20</v>
       </c>
       <c r="E189" s="42" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F189"/>
       <c r="G189"/>
@@ -19789,7 +19828,7 @@
         <v>20</v>
       </c>
       <c r="E191" s="42" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F191"/>
       <c r="G191"/>
@@ -19811,7 +19850,7 @@
         <v>20</v>
       </c>
       <c r="E192" s="42" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F192"/>
       <c r="G192"/>
@@ -19833,7 +19872,7 @@
         <v>20</v>
       </c>
       <c r="E193" s="42" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F193"/>
       <c r="G193"/>
@@ -19855,10 +19894,10 @@
         <v>20</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="E194" s="42" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F194"/>
       <c r="G194"/>
@@ -19881,10 +19920,10 @@
         <v>20</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E195" s="42" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F195"/>
       <c r="G195"/>
@@ -19907,7 +19946,7 @@
         <v>20</v>
       </c>
       <c r="E196" s="42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F196">
         <v>2</v>
@@ -19932,10 +19971,10 @@
         <v>20</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="E197" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F197" s="85"/>
       <c r="H197" s="31">
@@ -19957,10 +19996,10 @@
         <v>20</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="E198" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F198" s="85"/>
       <c r="H198" s="31">
@@ -19982,10 +20021,10 @@
         <v>20</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="E199" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F199" s="85"/>
       <c r="H199" s="31">
@@ -20007,7 +20046,7 @@
         <v>20</v>
       </c>
       <c r="E200" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F200"/>
       <c r="G200"/>
@@ -20015,7 +20054,7 @@
         <v>1455</v>
       </c>
       <c r="I200" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J200"/>
       <c r="K200"/>
@@ -20032,10 +20071,10 @@
         <v>20</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E201" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F201">
         <v>100</v>
@@ -20045,7 +20084,7 @@
         <v>860</v>
       </c>
       <c r="I201" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J201"/>
       <c r="K201"/>
@@ -20062,7 +20101,7 @@
         <v>20</v>
       </c>
       <c r="E202" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F202"/>
       <c r="G202"/>
@@ -20070,7 +20109,7 @@
         <v>80</v>
       </c>
       <c r="I202" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J202"/>
       <c r="K202"/>
@@ -20087,7 +20126,7 @@
         <v>20</v>
       </c>
       <c r="E203" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F203"/>
       <c r="G203"/>
@@ -20112,7 +20151,7 @@
         <v>20</v>
       </c>
       <c r="E204" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F204">
         <v>2</v>
@@ -20142,10 +20181,10 @@
         <v>20</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E205" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F205">
         <v>6</v>
@@ -20172,7 +20211,7 @@
         <v>20</v>
       </c>
       <c r="E206" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F206"/>
       <c r="G206"/>
@@ -20197,7 +20236,7 @@
         <v>20</v>
       </c>
       <c r="E207" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F207">
         <v>2</v>
@@ -20227,7 +20266,7 @@
         <v>20</v>
       </c>
       <c r="E208" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F208">
         <v>1</v>
@@ -20257,10 +20296,10 @@
         <v>20</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E209" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -20290,10 +20329,10 @@
         <v>20</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E210" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F210"/>
       <c r="G210"/>
@@ -20316,10 +20355,10 @@
         <v>20</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E211" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F211">
         <v>1</v>
@@ -20347,10 +20386,10 @@
         <v>20</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E212" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -20375,7 +20414,7 @@
         <v>20</v>
       </c>
       <c r="E213" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F213">
         <v>2.5</v>
@@ -20403,7 +20442,7 @@
         <v>20</v>
       </c>
       <c r="E214" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F214"/>
       <c r="G214"/>
@@ -20426,7 +20465,7 @@
         <v>24</v>
       </c>
       <c r="E215" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F215">
         <v>35</v>
@@ -20482,7 +20521,7 @@
         <v>24</v>
       </c>
       <c r="E217" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -20507,7 +20546,7 @@
         <v>24</v>
       </c>
       <c r="E218" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F218">
         <v>3</v>
@@ -20534,7 +20573,7 @@
         <v>24</v>
       </c>
       <c r="E219" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F219"/>
       <c r="G219"/>
@@ -20557,7 +20596,7 @@
         <v>26</v>
       </c>
       <c r="E220" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F220"/>
       <c r="G220"/>
@@ -20580,7 +20619,7 @@
         <v>24</v>
       </c>
       <c r="E221" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F221"/>
       <c r="G221"/>
@@ -20603,10 +20642,10 @@
         <v>24</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E222" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F222"/>
       <c r="G222"/>
@@ -20629,7 +20668,7 @@
         <v>24</v>
       </c>
       <c r="E223" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F223"/>
       <c r="G223"/>
@@ -20652,7 +20691,7 @@
         <v>24</v>
       </c>
       <c r="E224" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F224"/>
       <c r="G224"/>
@@ -20675,7 +20714,7 @@
         <v>24</v>
       </c>
       <c r="E225" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F225"/>
       <c r="G225"/>
@@ -20698,7 +20737,7 @@
         <v>24</v>
       </c>
       <c r="E226" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F226">
         <v>10</v>
@@ -20726,7 +20765,7 @@
         <v>25</v>
       </c>
       <c r="E227" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F227">
         <v>2</v>
@@ -20758,7 +20797,7 @@
         <v>25</v>
       </c>
       <c r="E228" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F228">
         <v>5</v>
@@ -20788,7 +20827,7 @@
         <v>25</v>
       </c>
       <c r="E229" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F229">
         <v>2</v>
@@ -20820,7 +20859,7 @@
         <v>25</v>
       </c>
       <c r="E230" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F230">
         <v>6</v>
@@ -20850,7 +20889,7 @@
         <v>25</v>
       </c>
       <c r="E231" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F231"/>
       <c r="G231"/>
@@ -20877,7 +20916,7 @@
         <v>25</v>
       </c>
       <c r="E232" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F232">
         <v>1</v>
@@ -20909,7 +20948,7 @@
         <v>25</v>
       </c>
       <c r="E233" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F233"/>
       <c r="G233"/>
@@ -20936,7 +20975,7 @@
         <v>25</v>
       </c>
       <c r="E234" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F234"/>
       <c r="G234"/>
@@ -20961,7 +21000,7 @@
         <v>25</v>
       </c>
       <c r="E235" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F235"/>
       <c r="G235"/>
@@ -20986,7 +21025,7 @@
         <v>25</v>
       </c>
       <c r="E236" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F236">
         <v>3</v>
@@ -20995,7 +21034,7 @@
         <v>350</v>
       </c>
       <c r="H236" s="31">
-        <f t="shared" ref="H236:H243" si="5">F236*G236</f>
+        <f t="shared" ref="H236:H243" si="6">F236*G236</f>
         <v>1050</v>
       </c>
       <c r="I236" t="s">
@@ -21016,7 +21055,7 @@
         <v>25</v>
       </c>
       <c r="E237" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F237">
         <v>6</v>
@@ -21025,7 +21064,7 @@
         <v>130</v>
       </c>
       <c r="H237" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>780</v>
       </c>
       <c r="I237" t="s">
@@ -21046,7 +21085,7 @@
         <v>25</v>
       </c>
       <c r="E238" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F238">
         <v>5</v>
@@ -21055,11 +21094,11 @@
         <v>620</v>
       </c>
       <c r="H238" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3100</v>
       </c>
       <c r="I238" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J238">
         <v>191</v>
@@ -21078,7 +21117,7 @@
         <v>25</v>
       </c>
       <c r="E239" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -21087,11 +21126,11 @@
         <v>400</v>
       </c>
       <c r="H239" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>800</v>
       </c>
       <c r="I239" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J239">
         <v>188</v>
@@ -21113,7 +21152,7 @@
         <v>25</v>
       </c>
       <c r="E240" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F240">
         <v>2</v>
@@ -21122,11 +21161,11 @@
         <v>250</v>
       </c>
       <c r="H240" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="I240" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J240">
         <v>188</v>
@@ -21145,7 +21184,7 @@
         <v>25</v>
       </c>
       <c r="E241" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F241">
         <v>8</v>
@@ -21154,11 +21193,11 @@
         <v>195</v>
       </c>
       <c r="H241" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1560</v>
       </c>
       <c r="I241" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J241">
         <v>189</v>
@@ -21177,7 +21216,7 @@
         <v>25</v>
       </c>
       <c r="E242" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F242">
         <v>2</v>
@@ -21186,11 +21225,11 @@
         <v>45</v>
       </c>
       <c r="H242" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>90</v>
       </c>
       <c r="I242" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J242">
         <v>190</v>
@@ -21209,7 +21248,7 @@
         <v>25</v>
       </c>
       <c r="E243" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F243">
         <v>2</v>
@@ -21218,11 +21257,11 @@
         <v>185</v>
       </c>
       <c r="H243" s="31">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>370</v>
       </c>
       <c r="I243" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J243"/>
       <c r="K243"/>
@@ -21239,7 +21278,7 @@
         <v>25</v>
       </c>
       <c r="E244" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F244"/>
       <c r="G244"/>
@@ -21247,7 +21286,7 @@
         <v>1195</v>
       </c>
       <c r="I244" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J244"/>
       <c r="K244"/>
@@ -21264,7 +21303,7 @@
         <v>25</v>
       </c>
       <c r="E245" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F245"/>
       <c r="G245"/>
@@ -21272,7 +21311,7 @@
         <v>700</v>
       </c>
       <c r="I245" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J245"/>
       <c r="K245"/>
@@ -21292,7 +21331,7 @@
         <v>25</v>
       </c>
       <c r="E246" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F246"/>
       <c r="G246"/>
@@ -21315,10 +21354,10 @@
         <v>29</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E247" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F247"/>
       <c r="G247"/>
@@ -21344,7 +21383,7 @@
         <v>29</v>
       </c>
       <c r="E248" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F248"/>
       <c r="G248"/>
@@ -21367,7 +21406,7 @@
         <v>29</v>
       </c>
       <c r="E249" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F249"/>
       <c r="G249"/>
@@ -21390,7 +21429,7 @@
         <v>29</v>
       </c>
       <c r="E250" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F250"/>
       <c r="G250"/>
@@ -21443,7 +21482,7 @@
         <v>29</v>
       </c>
       <c r="E252" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -21473,7 +21512,7 @@
         <v>29</v>
       </c>
       <c r="E253" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F253">
         <v>1</v>
@@ -21503,10 +21542,10 @@
         <v>29</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E254" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F254"/>
       <c r="G254"/>
@@ -21529,7 +21568,7 @@
         <v>29</v>
       </c>
       <c r="E255" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F255"/>
       <c r="G255"/>
@@ -21552,7 +21591,7 @@
         <v>29</v>
       </c>
       <c r="E256" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F256"/>
       <c r="G256"/>
@@ -21575,10 +21614,10 @@
         <v>29</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E257" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F257"/>
       <c r="G257"/>
@@ -21603,7 +21642,7 @@
         <v>29</v>
       </c>
       <c r="E258" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F258">
         <v>2</v>
@@ -21612,7 +21651,7 @@
         <v>2550</v>
       </c>
       <c r="H258" s="31">
-        <f t="shared" ref="H258:H299" si="6">F258*G258</f>
+        <f t="shared" ref="H258:H321" si="7">F258*G258</f>
         <v>5100</v>
       </c>
       <c r="I258"/>
@@ -21631,7 +21670,7 @@
         <v>29</v>
       </c>
       <c r="E259" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -21640,7 +21679,7 @@
         <v>700</v>
       </c>
       <c r="H259" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>700</v>
       </c>
       <c r="I259"/>
@@ -21684,7 +21723,7 @@
         <v>29</v>
       </c>
       <c r="E261" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F261" s="9"/>
       <c r="G261"/>
@@ -21707,7 +21746,7 @@
         <v>29</v>
       </c>
       <c r="E262" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F262"/>
       <c r="G262"/>
@@ -21732,7 +21771,7 @@
         <v>29</v>
       </c>
       <c r="E263" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F263"/>
       <c r="G263"/>
@@ -21757,7 +21796,7 @@
         <v>29</v>
       </c>
       <c r="E264" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F264"/>
       <c r="G264"/>
@@ -21784,7 +21823,7 @@
       </c>
       <c r="D265" s="67"/>
       <c r="E265" s="68" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F265" s="68">
         <v>5</v>
@@ -21834,10 +21873,10 @@
         <v>1</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E267" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F267"/>
       <c r="G267"/>
@@ -21865,7 +21904,7 @@
         <v>36</v>
       </c>
       <c r="E268" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F268">
         <v>1</v>
@@ -21890,7 +21929,7 @@
         <v>1</v>
       </c>
       <c r="E269" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F269"/>
       <c r="G269"/>
@@ -21913,7 +21952,7 @@
         <v>1</v>
       </c>
       <c r="E270" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F270"/>
       <c r="G270"/>
@@ -21936,7 +21975,7 @@
         <v>1</v>
       </c>
       <c r="E271" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F271"/>
       <c r="G271"/>
@@ -21958,7 +21997,7 @@
         <v>1</v>
       </c>
       <c r="E272" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F272"/>
       <c r="G272"/>
@@ -21983,7 +22022,7 @@
         <v>6</v>
       </c>
       <c r="E273" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F273"/>
       <c r="G273"/>
@@ -22006,7 +22045,7 @@
         <v>6</v>
       </c>
       <c r="E274" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F274"/>
       <c r="G274"/>
@@ -22029,7 +22068,7 @@
         <v>6</v>
       </c>
       <c r="E275" s="42" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H275" s="2">
         <v>405</v>
@@ -22049,7 +22088,7 @@
         <v>1</v>
       </c>
       <c r="E276" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F276">
         <v>2</v>
@@ -22076,7 +22115,7 @@
         <v>5</v>
       </c>
       <c r="E277" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F277">
         <v>1</v>
@@ -22103,7 +22142,7 @@
         <v>5</v>
       </c>
       <c r="E278" s="42" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F278" s="35">
         <v>16</v>
@@ -22156,7 +22195,7 @@
         <v>5</v>
       </c>
       <c r="E280" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -22210,7 +22249,7 @@
         <v>1</v>
       </c>
       <c r="E282" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F282"/>
       <c r="G282"/>
@@ -22218,7 +22257,7 @@
         <v>2120</v>
       </c>
       <c r="I282" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J282">
         <v>218</v>
@@ -22237,7 +22276,7 @@
         <v>8</v>
       </c>
       <c r="E283" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F283"/>
       <c r="G283"/>
@@ -22264,10 +22303,10 @@
         <v>8</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E284" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F284"/>
       <c r="G284"/>
@@ -22290,7 +22329,7 @@
         <v>8</v>
       </c>
       <c r="E285" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F285"/>
       <c r="G285"/>
@@ -22313,10 +22352,10 @@
         <v>8</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E286" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F286"/>
       <c r="G286"/>
@@ -22339,10 +22378,10 @@
         <v>8</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E287" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F287"/>
       <c r="G287"/>
@@ -22365,7 +22404,7 @@
         <v>8</v>
       </c>
       <c r="E288" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F288"/>
       <c r="G288"/>
@@ -22388,7 +22427,7 @@
         <v>8</v>
       </c>
       <c r="E289" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F289"/>
       <c r="G289"/>
@@ -22411,10 +22450,10 @@
         <v>9</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E290" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F290"/>
       <c r="G290"/>
@@ -22437,10 +22476,10 @@
         <v>9</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E291" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F291">
         <v>6</v>
@@ -22449,7 +22488,7 @@
         <v>90</v>
       </c>
       <c r="H291" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>540</v>
       </c>
       <c r="I291"/>
@@ -22491,10 +22530,10 @@
         <v>10</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E293" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F293">
         <v>1</v>
@@ -22519,7 +22558,7 @@
         <v>10</v>
       </c>
       <c r="E294" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F294"/>
       <c r="G294"/>
@@ -22542,7 +22581,7 @@
         <v>10</v>
       </c>
       <c r="E295" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F295"/>
       <c r="G295"/>
@@ -22565,7 +22604,7 @@
         <v>11</v>
       </c>
       <c r="E296" s="42" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F296" s="35">
         <v>5</v>
@@ -22574,11 +22613,11 @@
         <v>400</v>
       </c>
       <c r="H296" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2000</v>
       </c>
       <c r="I296" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J296"/>
       <c r="K296"/>
@@ -22595,7 +22634,7 @@
         <v>11</v>
       </c>
       <c r="E297" s="42" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F297" s="35">
         <v>2</v>
@@ -22604,11 +22643,11 @@
         <v>25</v>
       </c>
       <c r="H297" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="I297" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J297"/>
       <c r="K297"/>
@@ -22625,7 +22664,7 @@
         <v>11</v>
       </c>
       <c r="E298" s="42" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F298" s="35">
         <v>1</v>
@@ -22634,11 +22673,11 @@
         <v>200</v>
       </c>
       <c r="H298" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>200</v>
       </c>
       <c r="I298" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J298"/>
       <c r="K298"/>
@@ -22655,7 +22694,7 @@
         <v>11</v>
       </c>
       <c r="E299" s="42" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F299" s="35">
         <v>1</v>
@@ -22664,11 +22703,11 @@
         <v>250</v>
       </c>
       <c r="H299" s="31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="I299" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J299"/>
       <c r="K299"/>
@@ -22685,10 +22724,10 @@
         <v>12</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E300" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F300"/>
       <c r="G300"/>
@@ -22713,7 +22752,7 @@
         <v>12</v>
       </c>
       <c r="E301" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F301">
         <v>2</v>
@@ -22738,10 +22777,10 @@
         <v>12</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="E302" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F302"/>
       <c r="G302"/>
@@ -22764,7 +22803,7 @@
         <v>12</v>
       </c>
       <c r="E303" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F303"/>
       <c r="G303"/>
@@ -22787,10 +22826,10 @@
         <v>12</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E304" s="42" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H304" s="2">
         <v>2990</v>
@@ -22813,7 +22852,7 @@
         <v>12</v>
       </c>
       <c r="E305" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F305">
         <v>1</v>
@@ -22838,7 +22877,7 @@
         <v>12</v>
       </c>
       <c r="E306" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F306"/>
       <c r="G306"/>
@@ -22861,7 +22900,7 @@
         <v>12</v>
       </c>
       <c r="E307" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F307"/>
       <c r="G307"/>
@@ -22884,7 +22923,7 @@
         <v>12</v>
       </c>
       <c r="E308" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F308"/>
       <c r="G308"/>
@@ -22907,7 +22946,7 @@
         <v>12</v>
       </c>
       <c r="E309" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F309"/>
       <c r="G309"/>
@@ -22930,10 +22969,10 @@
         <v>12</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E310" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F310"/>
       <c r="G310"/>
@@ -22956,10 +22995,10 @@
         <v>12</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E311" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F311"/>
       <c r="G311"/>
@@ -22982,10 +23021,10 @@
         <v>12</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E312" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F312"/>
       <c r="G312"/>
@@ -23008,7 +23047,7 @@
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F313"/>
       <c r="G313"/>
@@ -23031,10 +23070,10 @@
         <v>12</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E314" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F314"/>
       <c r="G314"/>
@@ -23057,10 +23096,10 @@
         <v>13</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E315" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F315"/>
       <c r="G315"/>
@@ -23083,7 +23122,7 @@
         <v>13</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E316" t="s">
         <v>51</v>
@@ -23109,7 +23148,7 @@
         <v>13</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="E317" t="s">
         <v>69</v>
@@ -23135,7 +23174,7 @@
         <v>13</v>
       </c>
       <c r="E318" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F318"/>
       <c r="G318"/>
@@ -23158,7 +23197,7 @@
         <v>13</v>
       </c>
       <c r="E319" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="F319"/>
       <c r="G319"/>
@@ -23170,8 +23209,92 @@
       <c r="K319"/>
       <c r="L319"/>
     </row>
+    <row r="320" spans="1:12">
+      <c r="A320" s="9">
+        <v>331</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C320" s="41">
+        <v>13</v>
+      </c>
+      <c r="E320"/>
+      <c r="F320"/>
+      <c r="G320"/>
+      <c r="H320" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I320"/>
+      <c r="J320"/>
+      <c r="K320"/>
+      <c r="L320"/>
+    </row>
+    <row r="321" spans="1:12">
+      <c r="A321" s="9">
+        <v>332</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C321" s="41">
+        <v>13</v>
+      </c>
+      <c r="E321"/>
+      <c r="F321"/>
+      <c r="G321"/>
+      <c r="H321" s="31">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I321"/>
+      <c r="J321"/>
+      <c r="K321"/>
+      <c r="L321"/>
+    </row>
+    <row r="322" spans="1:12">
+      <c r="A322" s="9">
+        <v>2547</v>
+      </c>
+      <c r="B322"/>
+      <c r="C322" s="41">
+        <v>4</v>
+      </c>
+      <c r="D322"/>
+      <c r="I322"/>
+      <c r="J322"/>
+      <c r="K322"/>
+      <c r="L322"/>
+    </row>
+    <row r="323" spans="1:12">
+      <c r="A323" s="9">
+        <v>2548</v>
+      </c>
+      <c r="B323"/>
+      <c r="C323" s="41">
+        <v>4</v>
+      </c>
+      <c r="D323"/>
+      <c r="K323"/>
+      <c r="L323"/>
+    </row>
+    <row r="324" spans="1:12">
+      <c r="B324"/>
+      <c r="C324" s="41">
+        <v>4</v>
+      </c>
+      <c r="K324"/>
+      <c r="L324"/>
+    </row>
+    <row r="325" spans="1:12">
+      <c r="B325"/>
+      <c r="C325"/>
+      <c r="K325"/>
+      <c r="L325"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:J319" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A6:J324" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -23179,8 +23302,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6693B10-2773-4348-AFC6-DA49061F302D}">
-  <dimension ref="A1:P60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE83510F-50A8-44BF-90F0-633C1BFF0B11}">
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
@@ -23208,20 +23331,20 @@
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1">
       <c r="B1" s="86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C1" s="87">
-        <f>SUM(H2:H9)</f>
-        <v>233920</v>
+        <f>SUM(H2:H8)</f>
+        <v>329160</v>
       </c>
       <c r="F1" s="88" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G1" s="88" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H1" s="88" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I1" s="88"/>
       <c r="K1" s="88"/>
@@ -23234,15 +23357,15 @@
       </c>
       <c r="F2" s="89">
         <f>মাতবাখ!S2+মাদরাসা!U1</f>
-        <v>970140</v>
+        <v>1049300</v>
       </c>
       <c r="G2" s="89">
-        <f t="shared" ref="G2:G9" si="0">SUMIFS(C$11:C$1048576,D$11:D$1048576,E2)</f>
+        <f t="shared" ref="G2:G8" si="0">SUMIFS(C$10:C$1048576,D$10:D$1048576,E2)</f>
         <v>810000</v>
       </c>
       <c r="H2" s="89">
         <f>F2-G2</f>
-        <v>160140</v>
+        <v>239300</v>
       </c>
       <c r="J2" s="35"/>
       <c r="K2" s="31"/>
@@ -23255,15 +23378,15 @@
       </c>
       <c r="F3" s="89">
         <f>মাতবাখ!T2+মাদরাসা!U2</f>
-        <v>0</v>
+        <v>16080</v>
       </c>
       <c r="G3" s="89">
         <f t="shared" si="0"/>
         <v>16080</v>
       </c>
       <c r="H3" s="89">
-        <f t="shared" ref="H3:H7" si="1">F3-G3</f>
-        <v>-16080</v>
+        <f t="shared" ref="H3:H6" si="1">F3-G3</f>
+        <v>0</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="31"/>
@@ -23272,66 +23395,68 @@
     </row>
     <row r="4" spans="1:16" ht="26.45" customHeight="1">
       <c r="E4" s="7" t="s">
-        <v>358</v>
+        <v>33</v>
       </c>
       <c r="F4" s="89">
-        <f>মাতবাখ!U2+মাদরাসা!U2</f>
-        <v>0</v>
+        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E4)</f>
+        <v>163300</v>
       </c>
       <c r="G4" s="89">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H4" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K4" s="31"/>
+        <v>63300</v>
+      </c>
+      <c r="J4" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="26.45" customHeight="1">
       <c r="E5" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="89">
         <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E5)</f>
-        <v>163300</v>
+        <v>52000</v>
       </c>
       <c r="G5" s="89">
         <f t="shared" si="0"/>
-        <v>100000</v>
+        <v>26000</v>
       </c>
       <c r="H5" s="89">
         <f t="shared" si="1"/>
-        <v>63300</v>
-      </c>
-      <c r="J5" t="s">
-        <v>124</v>
-      </c>
+        <v>26000</v>
+      </c>
+      <c r="K5" s="31"/>
     </row>
     <row r="6" spans="1:16" ht="26.45" customHeight="1">
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F6" s="89">
-        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E6)</f>
-        <v>52000</v>
+        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E6)+মাদরাসা!U4</f>
+        <v>0</v>
       </c>
       <c r="G6" s="89">
         <f t="shared" si="0"/>
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="89">
         <f t="shared" si="1"/>
-        <v>26000</v>
-      </c>
-      <c r="K6" s="31"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="26.45" customHeight="1">
-      <c r="E7" s="7" t="s">
-        <v>359</v>
+      <c r="B7" s="9"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="F7" s="89">
-        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E7)+মাদরাসা!U4</f>
+        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E7)+মাদরাসা!U5</f>
         <v>0</v>
       </c>
       <c r="G7" s="89">
@@ -23339,220 +23464,214 @@
         <v>0</v>
       </c>
       <c r="H7" s="89">
-        <f t="shared" si="1"/>
+        <f>F7-G7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="26.45" customHeight="1">
-      <c r="B8" s="9"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>31</v>
+    <row r="8" spans="1:16" ht="22.9" customHeight="1">
+      <c r="E8" s="64" t="s">
+        <v>34</v>
       </c>
       <c r="F8" s="89">
-        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E8)+মাদরাসা!U5</f>
-        <v>0</v>
+        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E8)</f>
+        <v>45560</v>
       </c>
       <c r="G8" s="89">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45000</v>
       </c>
       <c r="H8" s="89">
         <f>F8-G8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="22.9" customHeight="1">
-      <c r="E9" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="89">
-        <f>SUMIFS(মাতবাখ!H:H,মাতবাখ!I:I,E9)</f>
-        <v>45560</v>
-      </c>
-      <c r="G9" s="89">
-        <f t="shared" si="0"/>
-        <v>45000</v>
-      </c>
-      <c r="H9" s="89">
-        <f>F9-G9</f>
         <v>560</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="22.15" customHeight="1">
-      <c r="A10" s="91"/>
-      <c r="B10" s="92" t="s">
+    <row r="9" spans="1:16" ht="22.15" customHeight="1">
+      <c r="A9" s="91"/>
+      <c r="B9" s="92" t="s">
         <v>360</v>
       </c>
-      <c r="C10" s="93" t="s">
+      <c r="C9" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="94" t="s">
+      <c r="D9" s="94" t="s">
         <v>361</v>
       </c>
-      <c r="E10" s="94" t="s">
+      <c r="E9" s="94" t="s">
         <v>362</v>
       </c>
-      <c r="G10" s="89"/>
+      <c r="G9" s="89"/>
+    </row>
+    <row r="10" spans="1:16" ht="17.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="95" t="s">
+        <v>363</v>
+      </c>
+      <c r="C10" s="96">
+        <v>100000</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="17.25">
       <c r="A11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" s="95" t="s">
         <v>363</v>
       </c>
-      <c r="C11" s="96">
-        <v>100000</v>
+      <c r="C11" s="97">
+        <v>300000</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>28</v>
       </c>
+      <c r="J11" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="17.25">
       <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" s="95" t="s">
-        <v>363</v>
-      </c>
-      <c r="C12" s="97">
-        <v>300000</v>
+        <v>3</v>
+      </c>
+      <c r="B12" s="98">
+        <v>46124</v>
+      </c>
+      <c r="C12" s="31">
+        <v>150000</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J12" t="s">
+      <c r="E12" s="97"/>
+      <c r="F12" t="s">
         <v>124</v>
       </c>
+      <c r="G12" s="7"/>
+      <c r="I12" s="7"/>
     </row>
     <row r="13" spans="1:16" ht="17.25">
       <c r="A13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" s="98">
-        <v>46124</v>
-      </c>
-      <c r="C13" s="31">
-        <v>150000</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="97"/>
+        <v>46125</v>
+      </c>
+      <c r="C13" s="97">
+        <v>45000</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>34</v>
+      </c>
       <c r="F13" t="s">
         <v>124</v>
       </c>
-      <c r="G13" s="7"/>
-      <c r="I13" s="7"/>
+      <c r="I13" s="1" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="17.25">
       <c r="A14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" s="98">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="C14" s="97">
-        <v>45000</v>
-      </c>
-      <c r="D14" s="64" t="s">
-        <v>34</v>
+        <v>26000</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="F14" t="s">
         <v>124</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="G14" t="s">
         <v>124</v>
       </c>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
     </row>
     <row r="15" spans="1:16" ht="17.25">
       <c r="A15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="98">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="C15" s="97">
-        <v>26000</v>
+        <v>110000</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" t="s">
-        <v>124</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="F15" s="35"/>
       <c r="G15" t="s">
         <v>124</v>
       </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="35"/>
     </row>
     <row r="16" spans="1:16" ht="17.25">
       <c r="A16">
-        <v>6</v>
-      </c>
-      <c r="B16" s="98">
-        <v>46127</v>
+        <v>7</v>
+      </c>
+      <c r="B16" s="95" t="s">
+        <v>364</v>
       </c>
       <c r="C16" s="97">
-        <v>110000</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="35"/>
-      <c r="G16" t="s">
+        <v>9720</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="17.25">
       <c r="A17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B17" s="95" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C17" s="97">
-        <v>9720</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>30</v>
+        <v>100000</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F17" t="s">
         <v>124</v>
       </c>
+      <c r="H17" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="17.25">
       <c r="A18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" s="95" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C18" s="97">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" t="s">
-        <v>124</v>
-      </c>
-      <c r="H18" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="17.25">
       <c r="A19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19" s="95" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C19" s="97">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>28</v>
@@ -23560,330 +23679,30 @@
     </row>
     <row r="20" spans="1:8" ht="17.25">
       <c r="A20">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B20" s="95" t="s">
-        <v>367</v>
-      </c>
-      <c r="C20" s="97">
-        <v>100000</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="17.25">
-      <c r="A21">
-        <v>11</v>
-      </c>
-      <c r="B21" s="95" t="s">
         <v>368</v>
       </c>
-      <c r="C21" s="96">
+      <c r="C20" s="96">
         <v>6360</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="D20" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E20" s="35" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="17.25">
-      <c r="A22">
-        <v>168</v>
-      </c>
-      <c r="B22" s="95"/>
-      <c r="C22" s="97"/>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" ht="17.25">
-      <c r="A23">
-        <v>169</v>
-      </c>
-      <c r="B23" s="95"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" ht="17.25">
-      <c r="A24">
-        <v>170</v>
-      </c>
-      <c r="B24" s="95"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" ht="17.25">
-      <c r="A25">
-        <v>171</v>
-      </c>
-      <c r="B25" s="95"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" ht="17.25">
-      <c r="A26">
-        <v>172</v>
-      </c>
-      <c r="B26" s="95"/>
-      <c r="C26" s="97"/>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" ht="17.25">
-      <c r="A27">
-        <v>173</v>
-      </c>
-      <c r="B27" s="95"/>
-      <c r="C27" s="97"/>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" ht="17.25">
-      <c r="A28">
-        <v>174</v>
-      </c>
-      <c r="B28" s="95"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" ht="17.25">
-      <c r="A29">
-        <v>175</v>
-      </c>
-      <c r="B29" s="95"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" ht="17.25">
-      <c r="A30">
-        <v>176</v>
-      </c>
-      <c r="B30" s="95"/>
-      <c r="C30" s="97"/>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" ht="17.25">
-      <c r="A31">
-        <v>177</v>
-      </c>
-      <c r="B31" s="95"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" ht="17.25">
-      <c r="A32">
-        <v>178</v>
-      </c>
-      <c r="B32" s="95"/>
-      <c r="C32" s="97"/>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="1:4" ht="17.25">
-      <c r="A33">
-        <v>179</v>
-      </c>
-      <c r="B33" s="95"/>
-      <c r="C33" s="97"/>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="1:4" ht="17.25">
-      <c r="A34">
-        <v>180</v>
-      </c>
-      <c r="B34" s="95"/>
-      <c r="C34" s="97"/>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="1:4" ht="17.25">
-      <c r="A35">
-        <v>181</v>
-      </c>
-      <c r="B35" s="95"/>
-      <c r="C35" s="97"/>
-      <c r="D35" s="1"/>
-    </row>
-    <row r="36" spans="1:4" ht="17.25">
-      <c r="A36">
-        <v>182</v>
-      </c>
-      <c r="B36" s="95"/>
-      <c r="C36" s="97"/>
-      <c r="D36" s="1"/>
-    </row>
-    <row r="37" spans="1:4" ht="17.25">
-      <c r="A37">
-        <v>183</v>
-      </c>
-      <c r="B37" s="95"/>
-      <c r="C37" s="97"/>
-      <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="1:4" ht="17.25">
-      <c r="A38">
-        <v>184</v>
-      </c>
-      <c r="B38" s="95"/>
-      <c r="C38" s="97"/>
-    </row>
-    <row r="39" spans="1:4" ht="17.25">
-      <c r="A39">
-        <v>185</v>
-      </c>
-      <c r="B39" s="95"/>
-      <c r="C39" s="97"/>
-    </row>
-    <row r="40" spans="1:4" ht="17.25">
-      <c r="A40">
-        <v>186</v>
-      </c>
-      <c r="B40" s="95"/>
-      <c r="C40" s="97"/>
-    </row>
-    <row r="41" spans="1:4" ht="17.25">
-      <c r="A41">
-        <v>187</v>
-      </c>
-      <c r="B41" s="95"/>
-      <c r="C41" s="97"/>
-    </row>
-    <row r="42" spans="1:4" ht="17.25">
-      <c r="A42">
-        <v>188</v>
-      </c>
-      <c r="B42" s="95"/>
-      <c r="C42" s="97"/>
-    </row>
-    <row r="43" spans="1:4" ht="17.25">
-      <c r="A43">
-        <v>189</v>
-      </c>
-      <c r="B43" s="95"/>
-      <c r="C43" s="97"/>
-    </row>
-    <row r="44" spans="1:4" ht="17.25">
-      <c r="A44">
-        <v>190</v>
-      </c>
-      <c r="B44" s="95"/>
-      <c r="C44" s="97"/>
-    </row>
-    <row r="45" spans="1:4" ht="17.25">
-      <c r="A45">
-        <v>191</v>
-      </c>
-      <c r="B45" s="95"/>
-      <c r="C45" s="97"/>
-    </row>
-    <row r="46" spans="1:4" ht="17.25">
-      <c r="A46">
-        <v>192</v>
-      </c>
-      <c r="B46" s="95"/>
-      <c r="C46" s="97"/>
-    </row>
-    <row r="47" spans="1:4" ht="17.25">
-      <c r="A47">
-        <v>193</v>
-      </c>
-      <c r="B47" s="95"/>
-      <c r="C47" s="97"/>
-    </row>
-    <row r="48" spans="1:4" ht="17.25">
-      <c r="A48">
-        <v>194</v>
-      </c>
-      <c r="B48" s="95"/>
-      <c r="C48" s="97"/>
-    </row>
-    <row r="49" spans="1:3" ht="17.25">
-      <c r="A49">
-        <v>195</v>
-      </c>
-      <c r="B49" s="95"/>
-      <c r="C49" s="97"/>
-    </row>
-    <row r="50" spans="1:3" ht="17.25">
-      <c r="A50">
-        <v>196</v>
-      </c>
-      <c r="B50" s="95"/>
-      <c r="C50" s="97"/>
-    </row>
-    <row r="51" spans="1:3" ht="17.25">
-      <c r="A51">
-        <v>197</v>
-      </c>
-      <c r="B51" s="95"/>
-      <c r="C51" s="97"/>
-    </row>
-    <row r="52" spans="1:3" ht="17.25">
-      <c r="A52">
-        <v>198</v>
-      </c>
-      <c r="B52" s="95"/>
-      <c r="C52" s="97"/>
-    </row>
-    <row r="53" spans="1:3" ht="17.25">
-      <c r="A53">
-        <v>199</v>
-      </c>
-      <c r="B53" s="95"/>
-      <c r="C53" s="97"/>
-    </row>
-    <row r="54" spans="1:3" ht="17.25">
-      <c r="A54">
-        <v>200</v>
-      </c>
-      <c r="B54" s="95"/>
-      <c r="C54" s="97"/>
-    </row>
-    <row r="55" spans="1:3" ht="17.25">
-      <c r="A55">
-        <v>201</v>
-      </c>
-      <c r="B55" s="95"/>
-      <c r="C55" s="97"/>
-    </row>
-    <row r="56" spans="1:3" ht="17.25">
-      <c r="A56">
-        <v>202</v>
-      </c>
-      <c r="B56" s="95"/>
-      <c r="C56" s="97"/>
-    </row>
-    <row r="57" spans="1:3" ht="17.25">
-      <c r="A57">
-        <v>203</v>
-      </c>
-      <c r="B57" s="95"/>
-      <c r="C57" s="97"/>
-    </row>
-    <row r="58" spans="1:3" ht="15.75">
-      <c r="A58">
-        <v>204</v>
-      </c>
-      <c r="B58" s="95"/>
-    </row>
-    <row r="59" spans="1:3" ht="15.75">
-      <c r="A59">
-        <v>205</v>
-      </c>
-      <c r="B59" s="95"/>
-    </row>
-    <row r="60" spans="1:3" ht="15.75">
-      <c r="A60">
-        <v>206</v>
-      </c>
-      <c r="B60" s="95"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A10:D61" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
+  <autoFilter ref="A9:D20" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3783D5-1D76-49AB-8B17-8DF62040DC74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FA768A-D565-4612-AEA5-5277F75B69A7}">
   <dimension ref="B1:U24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -23950,7 +23769,7 @@
       <c r="J5" s="109"/>
       <c r="K5" s="109"/>
       <c r="L5" s="110">
-        <f>SUM('[2]অর্থ গ্রহন'!$F$4:$G$4)</f>
+        <f>SUM('[1]অর্থ গ্রহন'!$F$4:$G$4)</f>
         <v>400000</v>
       </c>
       <c r="M5" s="111"/>
@@ -23994,8 +23813,8 @@
       <c r="J7" s="109"/>
       <c r="K7" s="109"/>
       <c r="L7" s="123">
-        <f>SUM('[2]অর্থ গ্রহন'!$F$6:$G$6)</f>
-        <v>505173</v>
+        <f>SUM('[1]অর্থ গ্রহন'!$F$6:$G$6)</f>
+        <v>760353</v>
       </c>
       <c r="M7" s="109"/>
       <c r="N7" s="103"/>
@@ -24005,7 +23824,7 @@
       <c r="R7" s="125"/>
       <c r="S7" s="126">
         <f>SUM(E10+L7)</f>
-        <v>3605817</v>
+        <v>3860997</v>
       </c>
       <c r="T7" s="125"/>
       <c r="U7" s="127"/>
@@ -24027,8 +23846,8 @@
       <c r="J8" s="109"/>
       <c r="K8" s="109"/>
       <c r="L8" s="132">
-        <f>SUM('[2]অর্থ গ্রহন'!$I$6:$J$6)</f>
-        <v>-105173</v>
+        <f>SUM('[1]অর্থ গ্রহন'!$I$6:$J$6)</f>
+        <v>-360353</v>
       </c>
       <c r="M8" s="132"/>
       <c r="N8" s="103"/>
@@ -24049,7 +23868,7 @@
       <c r="R9" s="134"/>
       <c r="S9" s="135">
         <f>SUM(E22+L8)</f>
-        <v>123103</v>
+        <v>-36837</v>
       </c>
       <c r="T9" s="134"/>
       <c r="U9" s="136"/>
@@ -24071,8 +23890,8 @@
       <c r="J10" s="142"/>
       <c r="K10" s="142"/>
       <c r="L10" s="143">
-        <f>SUM('[2]অর্থ গ্রহন'!$S$2:$T$2)</f>
-        <v>136375</v>
+        <f>SUM('[1]অর্থ গ্রহন'!$S$2:$T$2)</f>
+        <v>234675</v>
       </c>
       <c r="M10" s="143"/>
       <c r="N10" s="144"/>
@@ -24107,8 +23926,8 @@
       <c r="J12" s="111"/>
       <c r="K12" s="111"/>
       <c r="L12" s="154">
-        <f>SUM('[2]অর্থ গ্রহন'!$S$4:$T$4)</f>
-        <v>100000</v>
+        <f>SUM('[1]অর্থ গ্রহন'!$S$4:$T$4)</f>
+        <v>120000</v>
       </c>
       <c r="M12" s="154"/>
       <c r="N12" s="103"/>
@@ -24134,7 +23953,7 @@
       <c r="D14" s="156"/>
       <c r="E14" s="157">
         <f>SUM('বাকির হিসাব'!$C$1)</f>
-        <v>233920</v>
+        <v>329160</v>
       </c>
       <c r="F14" s="158"/>
       <c r="I14" s="155" t="s">
@@ -24144,7 +23963,7 @@
       <c r="K14" s="156"/>
       <c r="L14" s="159">
         <f>SUM(L10,L12)</f>
-        <v>236375</v>
+        <v>354675</v>
       </c>
       <c r="M14" s="156"/>
       <c r="N14" s="103"/>
@@ -24171,8 +23990,8 @@
       <c r="J16" s="111"/>
       <c r="K16" s="111"/>
       <c r="L16" s="132">
-        <f>SUM([2]বকেয়া!$K$1)</f>
-        <v>268798</v>
+        <f>SUM([1]বকেয়া!$K$1)</f>
+        <v>405678</v>
       </c>
       <c r="M16" s="132"/>
       <c r="N16" s="103"/>
@@ -24187,7 +24006,7 @@
       <c r="D17" s="111"/>
       <c r="E17" s="161">
         <f>SUM(মাদরাসা!$R$5)</f>
-        <v>0</v>
+        <v>76200</v>
       </c>
       <c r="F17" s="162"/>
       <c r="I17" s="102"/>
@@ -24197,13 +24016,13 @@
     </row>
     <row r="18" spans="2:21" ht="18.75">
       <c r="B18" s="153" t="s">
-        <v>278</v>
+        <v>138</v>
       </c>
       <c r="C18" s="111"/>
       <c r="D18" s="111"/>
       <c r="E18" s="161">
         <f>SUM(মাদরাসা!$R$2)</f>
-        <v>0</v>
+        <v>57160</v>
       </c>
       <c r="F18" s="162"/>
       <c r="I18" s="153" t="s">
@@ -24213,7 +24032,7 @@
       <c r="K18" s="111"/>
       <c r="L18" s="110">
         <f>L5-L14</f>
-        <v>163625</v>
+        <v>45325</v>
       </c>
       <c r="M18" s="111"/>
       <c r="N18" s="103"/>
@@ -24268,7 +24087,7 @@
       <c r="D22" s="113"/>
       <c r="E22" s="163">
         <f>SUM('অর্থ গ্রহণ'!X4:X5)</f>
-        <v>228276</v>
+        <v>323516</v>
       </c>
       <c r="F22" s="164"/>
       <c r="I22" s="165"/>
